--- a/public/air-request-template_NYG.xlsx
+++ b/public/air-request-template_NYG.xlsx
@@ -2364,22 +2364,22 @@
     <mergeCell ref="R1:AC1"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W1048576 AA2:AA1048576 R4:R1048576 R3 V3:V1048576 Z3:Z1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W1048576 AA3:AA1048576 R4:R1048576 R3 V3:V1048576 Z3:Z1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT("MASTER_CLAIM[CLAIM]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 B3:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT("MASTER_BRAND[BRAND_NAME]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>INDIRECT("MASTER_BU[BU]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>INDIRECT("MASTER_GARMENT_TYPE[DESCRIPTION]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2 N2 M3:M1048576" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3:M1048576" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>INDIRECT("MASTER_FACT[G]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N1048576 O2" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N3:N1048576" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>INDIRECT("MASTER_COUNTRY[SHIPTO_COUNTRY]")</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/air-request-template_NYG.xlsx
+++ b/public/air-request-template_NYG.xlsx
@@ -2365,7 +2365,7 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3:W1048576 AA3:AA1048576 R4:R1048576 R3 V3:V1048576 Z3:Z1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>INDIRECT("MASTER_CLAIM[CLAIM]")</formula1>
+      <formula1>"NYK,PROCUREMENT,PRODUCTION,COMMERCIAL,SCM NYG"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>INDIRECT("MASTER_BRAND[BRAND_NAME]")</formula1>
